--- a/artfynd/A 3155-2025 artfynd.xlsx
+++ b/artfynd/A 3155-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2091,6 +2091,115 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127667829</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjurstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>685338</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6560597</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3155-2025 artfynd.xlsx
+++ b/artfynd/A 3155-2025 artfynd.xlsx
@@ -2096,7 +2096,7 @@
         <v>127667829</v>
       </c>
       <c r="B14" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3155-2025 artfynd.xlsx
+++ b/artfynd/A 3155-2025 artfynd.xlsx
@@ -2096,7 +2096,7 @@
         <v>127667829</v>
       </c>
       <c r="B14" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3155-2025 artfynd.xlsx
+++ b/artfynd/A 3155-2025 artfynd.xlsx
@@ -2096,7 +2096,7 @@
         <v>127667829</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3155-2025 artfynd.xlsx
+++ b/artfynd/A 3155-2025 artfynd.xlsx
@@ -2096,7 +2096,7 @@
         <v>127667829</v>
       </c>
       <c r="B14" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3155-2025 artfynd.xlsx
+++ b/artfynd/A 3155-2025 artfynd.xlsx
@@ -2205,7 +2205,7 @@
         <v>131997705</v>
       </c>
       <c r="B15" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 3155-2025 artfynd.xlsx
+++ b/artfynd/A 3155-2025 artfynd.xlsx
@@ -2205,7 +2205,7 @@
         <v>131997705</v>
       </c>
       <c r="B15" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>131997780</v>
       </c>
       <c r="B16" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>131997655</v>
       </c>
       <c r="B17" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>131997810</v>
       </c>
       <c r="B18" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 3155-2025 artfynd.xlsx
+++ b/artfynd/A 3155-2025 artfynd.xlsx
@@ -2205,7 +2205,7 @@
         <v>131997705</v>
       </c>
       <c r="B15" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>131997780</v>
       </c>
       <c r="B16" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>131997655</v>
       </c>
       <c r="B17" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>131997810</v>
       </c>
       <c r="B18" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 3155-2025 artfynd.xlsx
+++ b/artfynd/A 3155-2025 artfynd.xlsx
@@ -2205,7 +2205,7 @@
         <v>131997705</v>
       </c>
       <c r="B15" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 3155-2025 artfynd.xlsx
+++ b/artfynd/A 3155-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87858109</v>
+        <v>87857802</v>
       </c>
       <c r="B2" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685462.0932504087</v>
+        <v>685499</v>
       </c>
       <c r="R2" t="n">
-        <v>6560302.125402788</v>
+        <v>6560344</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,19 +747,9 @@
           <t>2020-08-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>87858829</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685419.170960453</v>
+        <v>685419</v>
       </c>
       <c r="R3" t="n">
-        <v>6560327.27490565</v>
+        <v>6560327</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +849,9 @@
           <t>2020-08-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,57 +879,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87857802</v>
+        <v>100782420</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klovkällsmossen, Srm</t>
+          <t>S Garpängen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685498.667861099</v>
+        <v>685437</v>
       </c>
       <c r="R4" t="n">
-        <v>6560343.988070657</v>
+        <v>6560290</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,69 +977,63 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>92556248</v>
+        <v>96304476</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Garpängen, Srm</t>
+          <t>Ö Garpängen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685390.5344197073</v>
+        <v>685762</v>
       </c>
       <c r="R5" t="n">
-        <v>6560323.313292548</v>
+        <v>6560514</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,22 +1057,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-04-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-04-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92556226</v>
+        <v>96305919</v>
       </c>
       <c r="B6" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,27 +1101,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685390.2353595474</v>
+        <v>685457</v>
       </c>
       <c r="R6" t="n">
-        <v>6560329.465487645</v>
+        <v>6560535</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,22 +1158,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-04-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-04-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På  tallraka i nedre delen av barrskogssluttning som avslutas i fuktig miljö.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95066066</v>
+        <v>87858109</v>
       </c>
       <c r="B7" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1207,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685590.8352738663</v>
+        <v>685462</v>
       </c>
       <c r="R7" t="n">
-        <v>6560333.055251773</v>
+        <v>6560302</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,22 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,12 +1286,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1380,12 +1301,7 @@
         <v>96152986</v>
       </c>
       <c r="B8" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685390.0804313144</v>
+        <v>685390</v>
       </c>
       <c r="R8" t="n">
-        <v>6560311.471625882</v>
+        <v>6560311</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1453,19 +1369,9 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,37 +1399,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96304476</v>
+        <v>131997705</v>
       </c>
       <c r="B9" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>366</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,17 +1433,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ö Garpängen, Srm</t>
+          <t>NO Klovkällsmossen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685762.2014168701</v>
+        <v>685503</v>
       </c>
       <c r="R9" t="n">
-        <v>6560514.064185243</v>
+        <v>6560526</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1566,22 +1467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,15 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96304522</v>
+        <v>127667829</v>
       </c>
       <c r="B10" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,38 +1511,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Garpängen, Srm</t>
+          <t>Tjurstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685479.9490871002</v>
+        <v>685338</v>
       </c>
       <c r="R10" t="n">
-        <v>6560379.563921786</v>
+        <v>6560597</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1683,22 +1577,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,7 +1591,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1726,15 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96305919</v>
+        <v>131997655</v>
       </c>
       <c r="B11" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,40 +1620,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Garpängen, Srm</t>
+          <t>NO Klovkällsmossen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685456.9873072024</v>
+        <v>685499</v>
       </c>
       <c r="R11" t="n">
-        <v>6560534.152304919</v>
+        <v>6560542</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,27 +1686,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På  tallraka i nedre delen av barrskogssluttning som avslutas i fuktig miljö.</t>
+          <t>Några flisor vid roten på en torrgran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,7 +1705,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1847,53 +1723,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98483649</v>
+        <v>131997780</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Garpängen, Srm</t>
+          <t>NO Klovkällsmossen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685434.0156654585</v>
+        <v>685668</v>
       </c>
       <c r="R12" t="n">
-        <v>6560381.955231995</v>
+        <v>6560457</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1920,27 +1800,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På stående död gran.</t>
+          <t>Bearbetad tallraka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,7 +1819,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1968,15 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100782420</v>
+        <v>131997810</v>
       </c>
       <c r="B13" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,46 +1848,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>S Garpängen, Srm</t>
+          <t>NO Klovkällsmossen, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685436.9369633145</v>
+        <v>685708</v>
       </c>
       <c r="R13" t="n">
-        <v>6560290.110285221</v>
+        <v>6560519</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2050,22 +1914,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-05-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +1933,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2093,10 +1951,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127667829</v>
+        <v>92556226</v>
       </c>
       <c r="B14" t="n">
-        <v>57670</v>
+        <v>111390</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,46 +1962,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjurstaskogen, Srm</t>
+          <t>Garpängen, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685338</v>
+        <v>685390</v>
       </c>
       <c r="R14" t="n">
-        <v>6560597</v>
+        <v>6560329</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2170,12 +2020,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2021-04-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2021-04-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,6 +2034,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2202,51 +2053,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131997705</v>
+        <v>95066066</v>
       </c>
       <c r="B15" t="n">
-        <v>91872</v>
+        <v>111390</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>219711</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO Klovkällsmossen, Srm</t>
+          <t>Klovkällsmossen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685503</v>
+        <v>685590</v>
       </c>
       <c r="R15" t="n">
-        <v>6560526</v>
+        <v>6560333</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2270,12 +2122,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,60 +2155,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131997780</v>
+        <v>96304522</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>106244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NO Klovkällsmossen, Srm</t>
+          <t>Garpängen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685668</v>
+        <v>685480</v>
       </c>
       <c r="R16" t="n">
-        <v>6560457</v>
+        <v>6560380</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2380,17 +2224,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Bearbetad tallraka.</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,6 +2238,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2417,60 +2257,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131997655</v>
+        <v>92556248</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO Klovkällsmossen, Srm</t>
+          <t>Garpängen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685499</v>
+        <v>685391</v>
       </c>
       <c r="R17" t="n">
-        <v>6560542</v>
+        <v>6560323</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2494,17 +2326,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2021-04-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Några flisor vid roten på en torrgran.</t>
+          <t>2021-04-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,6 +2340,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2528,120 +2356,6 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>131997810</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57950</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>NO Klovkällsmossen, Srm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>685708</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6560519</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Österhaninge</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Granlåga.</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3155-2025 artfynd.xlsx
+++ b/artfynd/A 3155-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87858829</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100782420</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96305919</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87858109</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96152986</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127667829</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92556226</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96304522</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1608,6 +1653,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92556248</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,6 +1760,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87857802</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96304476</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131997705</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2026,6 +2091,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131997655</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131997780</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2254,6 +2329,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131997810</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2356,8 +2436,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95066066</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>